--- a/astro-site/public/dl/mobile-bar-business-plan/mobile-bar-startup-checklist.xlsx
+++ b/astro-site/public/dl/mobile-bar-business-plan/mobile-bar-startup-checklist.xlsx
@@ -598,12 +598,12 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Choose your structure with your accountant: single-member LLC, sole proprietor or S corp</t>
+          <t>Pick your legal model: dry hire by default (your client buys the alcohol; you bring the bar, the bartenders and everything else) or licensed full-service</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Owner / Accountant</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>An LLC separates your personal assets from business liability, which matters when you work at weddings with alcohol on site. An S corp election can lower self-employment tax once profit is steady; ask your accountant when it pays off.</t>
+          <t>Dry hire means the host buys and owns the alcohol and you sell service only. Full-service needs a licensed partner, your own license tied to a location, or a per-event permit. Your choice decides Phase 2; ask your state ABC before you advertise either one.</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Get your free EIN from the IRS and register for state payroll and unemployment tax</t>
+          <t>Hire an accountant or bookkeeper and set up quarterly estimated taxes</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -635,12 +635,12 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>Weeks 1-2</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Apply online at irs.gov; it is free and takes minutes. Then register with your state workforce agency before your first hire, so your payroll provider can file W-2 bartenders from day one.</t>
+          <t>Ask for experience with event or service businesses. Estimated taxes are due quarterly; move a share of every deposit into a tax savings account so the bill never surprises you.</t>
         </is>
       </c>
     </row>
@@ -652,22 +652,22 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Register your LLC with the Secretary of State, appoint a registered agent and sign an operating agreement</t>
+          <t>Choose your structure with your accountant: single-member LLC, sole proprietor or S corp</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>Owner / Attorney</t>
+          <t>Owner / Accountant</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Weeks 2-3</t>
+          <t>Week 1</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>File the articles of organization on your Secretary of State website. Fees and processing times vary by state. Sign an operating agreement even if you are the only member; venues and banks may ask for it.</t>
+          <t>An LLC separates your personal assets from business liability, which matters when you work at weddings with alcohol on site. An S corp election can lower self-employment tax once profit is steady; ask your accountant when it pays off.</t>
         </is>
       </c>
     </row>
@@ -679,22 +679,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Open a business bank account and keep your finances separate</t>
+          <t>Register your LLC with the Secretary of State, appoint a registered agent and sign an operating agreement</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Attorney</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>Weeks 2-3</t>
+          <t>Weeks 1-2</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Bring your EIN letter and formation documents. Use one card for purchases and a separate account for client deposits, so event deposits never mix with personal money.</t>
+          <t>File the articles of organization on your Secretary of State website. Fees and processing times vary by state. Sign an operating agreement even if you are the only member; venues and banks may ask for it.</t>
         </is>
       </c>
     </row>
@@ -706,22 +706,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Get your seller's permit (sales tax permit) and find out if bar service is taxable in your state</t>
+          <t>Get your free EIN for the LLC from the IRS and register for state payroll and unemployment tax</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Owner / Accountant</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Weeks 2-4</t>
+          <t>Weeks 2-3</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Apply with your state tax agency (California: cdtfa.ca.gov). In some states the whole invoice is taxable, including bartender service and rentals. Confirm the rule and whether service charges are taxed before you quote.</t>
+          <t>Apply online at irs.gov once the LLC is filed; it is free and takes minutes. Then register with your state workforce agency before your first hire, so your payroll provider can file W-2 bartenders from day one.</t>
         </is>
       </c>
     </row>
@@ -733,7 +733,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Apply for the city or county business license, plus a DBA if you use a trade name</t>
+          <t>Open a business bank account and keep your finances separate</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -743,12 +743,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>Weeks 2-4</t>
+          <t>Weeks 2-3</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Check every city where you plan to work: some require a license to operate there. A DBA (fictitious business name) is filed with the county or the state. Keep copies for venue paperwork.</t>
+          <t>Bring your EIN letter and formation documents. Use one card for purchases and a separate account for client deposits, so event deposits never mix with personal money.</t>
         </is>
       </c>
     </row>
@@ -760,22 +760,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Hire an accountant or bookkeeper and set up quarterly estimated taxes</t>
+          <t>Get your seller's permit (sales tax permit) and find out if bar service is taxable in your state</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Owner / Accountant</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Weeks 3-4</t>
+          <t>Weeks 2-4</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Ask for experience with event or service businesses. Estimated taxes are due quarterly; move a share of every deposit into a tax savings account so the bill never surprises you.</t>
+          <t>Apply with your state tax agency (California: cdtfa.ca.gov). In some states the whole invoice is taxable, including bartender service and rentals. Confirm the rule and whether service charges are taxed before you quote.</t>
         </is>
       </c>
     </row>
@@ -787,7 +787,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Choose booking software and a CRM for proposals, e-signed contracts, deposits and balances</t>
+          <t>Apply for the city or county business license, plus a DBA if you use a trade name</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -797,12 +797,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>Weeks 3-5</t>
+          <t>Weeks 2-4</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>One tool should send the quote, collect the e-signature and take the deposit by card. Test it with a mock proposal before you pay for a full year.</t>
+          <t>Check every city where you plan to work: some require a license to operate there. A DBA (fictitious business name) is filed with the county or the state. Keep copies for venue paperwork.</t>
         </is>
       </c>
     </row>
@@ -814,49 +814,49 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
+          <t>Choose booking software and a CRM for proposals, e-signed contracts, deposits and balances</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Weeks 3-5</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>One tool should send the quote, collect the e-signature and take the deposit by card. Test it with a mock proposal before you pay for a full year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="119.75" customHeight="1">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>☐</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
           <t>Have an attorney draft your service agreement with dry-hire clauses</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C14" s="11" t="inlineStr">
         <is>
           <t>Owner / Attorney</t>
         </is>
       </c>
-      <c r="D13" s="5" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Weeks 3-6</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Cover: the host buys and owns the alcohol and keeps any leftovers; no cash bar, drink tickets, ticketed entry that includes drinks or donations; gratuity agreed in writing; deposit and tiered cancellation; guest count changes; power access; photo use. Ask your attorney to check it against your state ABC rules.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="89.75" customHeight="1">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
-      </c>
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Pick your legal model: dry hire by default (you supply the alcohol; we bring the bar, the bartenders and everything else) or licensed full-service</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="D14" s="11" t="inlineStr">
-        <is>
-          <t>Weeks 4-6</t>
-        </is>
-      </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>Dry hire means the host buys and owns the alcohol and you sell service only. Full-service needs a licensed partner, your own license tied to a location, or a per-event permit. Your choice decides Phase 2; ask your state ABC before you advertise either one.</t>
+          <t>Cover: the host buys and owns the alcohol and keeps any leftovers; no cash bar, drink tickets, ticketed entry that includes drinks or donations; gratuity terms in writing where your state allows them; deposit and tiered cancellation; guest count changes; power access; photo use. Ask your attorney to check it against your state ABC rules.</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>Look for roughly 160-270 sq ft with drive-up access and room to hitch. Ask about 24-hour access, power for charging, insurance requirements and the deposit. Check your HOA or city rules on parking a trailer at home.</t>
+          <t>Look for roughly 160-270 sq ft (15-25 sq m) with drive-up access and room to hitch. Ask about 24-hour access, power for charging, insurance requirements and the deposit. Check your HOA or city rules on parking a trailer at home.</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>There is no mobile bar permit in most counties, so ask by phone or email whether mobile food vendor rules apply to you. Ask if cut garnish needs a licensed base, and whether a hand sink in the trailer is required. Use only commercial bagged ice.</t>
+          <t>There is no mobile bar permit in most counties, so ask by phone or email whether mobile food vendor rules apply to you. Ask if cut garnish needs a licensed commissary, and whether a hand sink in the trailer is required. Use only commercial bagged ice.</t>
         </is>
       </c>
     </row>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>In dry hire the organizer usually holds the special event permit. If you ever serve alcohol under your own license, you need a temporary or special event permit from your state ABC. Get the answer in writing.</t>
+          <t>In dry hire the organizer usually holds the special event permit. If you ever serve alcohol under your own license, you may need a temporary or special event permit from your state ABC. Get the answer in writing.</t>
         </is>
       </c>
     </row>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Buy a used bar trailer: 6 x 12 ft cargo, concession or horse trailer, with an inspection</t>
+          <t>Buy a used bar trailer: 6 x 12 ft (1.8 x 3.7 m) cargo, concession or horse trailer, with an inspection</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -1167,7 +1167,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Title and register the trailer with your state DMV and add commercial auto cover</t>
+          <t>Title and register the trailer with your state DMV and add commercial auto coverage</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>Insure your gear in transit with inland marine (equipment floater) cover</t>
+          <t>Insure your gear in transit with inland marine (equipment floater) coverage</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Set up a commercial bagged-ice supplier and buy ice bins and coolers (60 lb ice bins)</t>
+          <t>Set up a commercial bagged-ice supplier and buy ice bins (60 lb (27 kg))</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Install LED lighting and an inverter generator, then load-test with everything on</t>
+          <t>Install the inverter generator and load-test the trailer with everything on</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Plug in lights, fridge, pumps and speaker for 30 minutes and watch the load. Many venues require a quiet generator or ask for a shore power connection, so get both options ready.</t>
+          <t>Plug in lights, fridge, pumps and speaker for 30 minutes and watch the load. Many venues require a quiet generator or ask for a dedicated venue outlet, so get both options ready.</t>
         </is>
       </c>
     </row>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>Compare unit prices per fl oz. Ask for a business account and tax-exempt resale paperwork where you resell supplies. Buy in bulk for syrups and juices that keep.</t>
+          <t>Compare unit prices per fl oz. Ask for a business account and a resale certificate where you resell supplies. Buy in bulk for syrups and juices that keep.</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>Weeks 12-14</t>
+          <t>Weeks 14-15</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
@@ -1915,7 +1915,7 @@
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>These ratios are a Kit estimate; adjust after your first events. Add one barback when the event has over 150 guests or two stations. Use the Staffing tab to cost each event.</t>
+          <t>These ratios are a Kit estimate; adjust after your first events. Add one barback when the event has over 150 guests or two stations. Use the Pricing Calculator to cost each event.</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Sign up with a payroll provider and bind your workers' comp policy</t>
+          <t>Sign up with a payroll provider and link your workers' comp policy to payroll</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -2050,7 +2050,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>Minimum serving ages and permit rules differ by state, and sometimes by county. Ask your state ABC and county health department. If a food handler card is required, get it for every crew member.</t>
+          <t>Minimum serving ages and permit rules differ by state, and sometimes by county. Ask your state ABC and county health department. If a food handler card is required, get it for every crew member. Some cities and counties also require a bartender or alcohol server permit: ask them too.</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="E14" s="11" t="inlineStr">
         <is>
-          <t>A service charge is part of the invoice and is taxable income; a voluntary gratuity belongs to staff. Add a tip jar only where your state does not treat tips as a sale (Missouri may). Put the gratuity terms in the contract.</t>
+          <t>A service charge is part of the invoice and is taxable income; a voluntary gratuity belongs to staff. Add a tip jar or a gratuity line only where your state does not treat it as a sale (Missouri may).</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2457,7 @@
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Offer a first-look rate or a referral thank-you. Ask venues to put you on their preferred vendor list and send a thank-you gift after the first booking.</t>
+          <t>Offer an introductory rate or a referral thank-you. Ask venues to put you on their preferred vendor list and send a thank-you gift after the first booking.</t>
         </is>
       </c>
     </row>
@@ -2538,7 +2538,7 @@
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>Use the calculator to get your cost per guest and minimum. Send each quote within 24 hours and follow up after 3 days.</t>
+          <t>Use the calculator to get your cost per guest and price per guest; your minimum is an input there. Send each quote within 24 hours and follow up after 3 days.</t>
         </is>
       </c>
     </row>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Hold a client briefing at D-21: guests, hours, package, specialty bar, venue and restrictions</t>
+          <t>Hold a client briefing 3 weeks before the event: guests, hours, package, specialty bar, venue and restrictions</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>D-21</t>
+          <t>3 weeks out</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -2741,7 +2741,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>Visit the venue or hold a tech call at D-14: trailer access, power, water and venue rules</t>
+          <t>Do a site visit or walkthrough call 2 weeks out: trailer access, power, water and venue rules</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>D-14</t>
+          <t>2 weeks out</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Send the host the shopping list at D-14 and buy mixers, garnish and ice at D-1</t>
+          <t>Send the host the shopping list 2 weeks out and buy mixers, garnish and ice the day before</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>D-14 and D-1</t>
+          <t>2 weeks out + day before</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -2795,22 +2795,22 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Run the trailer load-out checklist: hitch, lights and glass secured</t>
+          <t>Invoice the balance before the event and track deposits</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Lead bartender</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>D-1</t>
+          <t>1 week to 1 day before</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>Check hitch pin, safety chains, tire pressure and brake lights. Strap down crates and racks. Photograph the packed trailer.</t>
+          <t>Send the final invoice a week out. Mark deposits as paid and keep any service charge as a separate line; add a gratuity line only where your state does not treat it as a sale.</t>
         </is>
       </c>
     </row>
@@ -2822,22 +2822,22 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Set up 60-120 minutes early, serve the event and call last call</t>
+          <t>Run the trailer load-out checklist: hitch, lights and glass secured</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Lead bartender / Crew</t>
+          <t>Lead bartender</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Event day</t>
+          <t>Day before</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
-          <t>Arrive on time, test the lights, power and water, then set the bar. Announce last call 15-30 minutes before closing, as agreed with the host.</t>
+          <t>Check hitch pin, safety chains, tire pressure and brake lights. Strap down crates and racks. Photograph the packed trailer.</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Break down, count the glassware, hand leftover alcohol back to the host and return rentals</t>
+          <t>Set up 60-120 minutes early, serve the event and call last call</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>The host owns the leftover alcohol, so pack it as theirs and sign for the count. Clean the trailer, count glass and return rentals by the agreed return time.</t>
+          <t>Arrive on time, test the lights, power and water, then set the bar. Announce last call 15-30 minutes before closing, as agreed with the host.</t>
         </is>
       </c>
     </row>
@@ -2876,22 +2876,22 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Invoice the balance before the event, track deposits and put the agreed gratuity on the invoice</t>
+          <t>Break down, count the glassware, hand leftover alcohol back to the host and return rentals</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Lead bartender / Crew</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>D-7 to D-1</t>
+          <t>Event day</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>Send the final invoice a week out. Mark deposits as paid and keep service charge and gratuity as separate lines.</t>
+          <t>The host owns the leftover alcohol, so pack it as theirs and sign for the count. Clean the trailer, count glass and return rentals by the agreed return time.</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>D+2</t>
+          <t>2 days after</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
